--- a/Resultados Test.xlsx
+++ b/Resultados Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFM_NEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4F1D87-8B53-49A4-AE8A-D3DDE4D6DB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361650AF-2AB5-428F-A419-463A2436BB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-2055" windowWidth="38640" windowHeight="21120" xr2:uid="{B1C3D829-37D9-454F-9F7F-CDE7CD3158AE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="82">
   <si>
     <t>Class</t>
   </si>
@@ -80,145 +80,208 @@
     <t>scratches</t>
   </si>
   <si>
-    <t>Speed: 0.3ms preprocess, 9.3ms inference, 0.0ms loss, 1.6ms postprocess per image</t>
-  </si>
-  <si>
-    <t>0.691</t>
-  </si>
-  <si>
-    <t>0.685</t>
+    <t>    epochs=100,</t>
+  </si>
+  <si>
+    <t>    imgsz=448,</t>
+  </si>
+  <si>
+    <t>    batch=16,</t>
+  </si>
+  <si>
+    <t>    name='tfm_steel_aimgsz_448_mixup_0-5',</t>
+  </si>
+  <si>
+    <t>    device=0</t>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <t>Config</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model = YOLO('yolov8n,pt') </t>
+  </si>
+  <si>
+    <t xml:space="preserve">model = YOLO('yolov8s,pt') </t>
+  </si>
+  <si>
+    <t>results = model,train(</t>
+  </si>
+  <si>
+    <t>    data=',,/dataset_config,yaml',  # El nuevo nombre que le hemos dado</t>
+  </si>
+  <si>
+    <t>    mixup=0,5,    # Un toque de MixUp suele ayudar más en acero</t>
+  </si>
+  <si>
+    <t>    hsv_h=0,015,   # Cambia el tono (color) un poco</t>
+  </si>
+  <si>
+    <t>    hsv_s=0,7,     # Cambia la saturación</t>
+  </si>
+  <si>
+    <t>Speed: 0,3ms preprocess, 9,3ms inference, 0,0ms loss, 1,6ms postprocess per image</t>
+  </si>
+  <si>
+    <t>    hsv_v=0,4,     # Cambia el brillo (muy útil para reflejos en el acero)</t>
+  </si>
+  <si>
+    <t>    degrees=10,0,  # Rota las imágenes hasta 10 grados (recalcula etiquetas solo)</t>
+  </si>
+  <si>
+    <t>    translate=0,1, # Mueve la imagen un 10% (mueve etiquetas también)</t>
+  </si>
+  <si>
+    <t>    scale=0,5,     # Zoom hacia afuera/adentro</t>
+  </si>
+  <si>
+    <t>    flipud=0,5,    # Volteo vertical (50% de probabilidad)</t>
+  </si>
+  <si>
+    <t>    fliplr=0,5,    # Volteo horizontal (50% de probabilidad)</t>
+  </si>
+  <si>
+    <t>    mosaic=1,0,    # Mezcla 4 imágenes en una (ya lo hacía, pero aquí lo confirmas)</t>
+  </si>
+  <si>
+    <t>Comparativa Nano vs Small</t>
+  </si>
+  <si>
+    <t>results = model.train(</t>
+  </si>
+  <si>
+    <t>    data='../dataset_config.yaml',  # El nuevo nombre que le hemos dado</t>
+  </si>
+  <si>
+    <t>    imgsz=640,</t>
+  </si>
+  <si>
+    <t>    batch=32,</t>
+  </si>
+  <si>
+    <t>    optimizer='AdamW',  # &lt;--- Optimizador más inteligente</t>
+  </si>
+  <si>
+    <t>    label_smoothing=0.1,</t>
+  </si>
+  <si>
+    <t>    mixup=0.5,    # Un toque de MixUp suele ayudar más en acero</t>
+  </si>
+  <si>
+    <t>    hsv_h=0.015,   # Cambia el tono (color) un poco</t>
+  </si>
+  <si>
+    <t>    hsv_s=0.7,     # Cambia la saturación</t>
+  </si>
+  <si>
+    <t>    hsv_v=0.4,     # Cambia el brillo (muy útil para reflejos en el acero)</t>
+  </si>
+  <si>
+    <t>    degrees=10.0,  # Rota las imágenes hasta 10 grados (recalcula etiquetas solo)</t>
+  </si>
+  <si>
+    <t>    translate=0.1, # Mueve la imagen un 10% (mueve etiquetas también)</t>
+  </si>
+  <si>
+    <t>    scale=0.5,     # Zoom hacia afuera/adentro</t>
+  </si>
+  <si>
+    <t>    flipud=0.5,    # Volteo vertical (50% de probabilidad)</t>
+  </si>
+  <si>
+    <t>    fliplr=0.5,    # Volteo horizontal (50% de probabilidad)</t>
+  </si>
+  <si>
+    <t>    mosaic=1.0,    # Mezcla 4 imágenes en una (ya lo hacía, pero aquí lo confirmas)</t>
+  </si>
+  <si>
+    <t>    name='tfm_steel_aimgsz_640_AdaW_yolov8s',</t>
+  </si>
+  <si>
+    <t>0.648</t>
+  </si>
+  <si>
+    <t>0.699</t>
   </si>
   <si>
     <t>0.729</t>
   </si>
   <si>
-    <t>0.403</t>
-  </si>
-  <si>
-    <t>0.507</t>
-  </si>
-  <si>
-    <t>0.257</t>
-  </si>
-  <si>
-    <t>0.428</t>
-  </si>
-  <si>
-    <t>0.175</t>
-  </si>
-  <si>
-    <t>0.636</t>
-  </si>
-  <si>
-    <t>0.726</t>
-  </si>
-  <si>
-    <t>0.721</t>
-  </si>
-  <si>
-    <t>0.382</t>
-  </si>
-  <si>
-    <t>0.777</t>
-  </si>
-  <si>
-    <t>0.925</t>
-  </si>
-  <si>
-    <t>0.927</t>
-  </si>
-  <si>
-    <t>0.587</t>
-  </si>
-  <si>
-    <t>0.847</t>
-  </si>
-  <si>
-    <t>0.697</t>
-  </si>
-  <si>
-    <t>0.783</t>
-  </si>
-  <si>
-    <t>0.496</t>
-  </si>
-  <si>
-    <t>0.566</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>0.276</t>
-  </si>
-  <si>
-    <t>0.814</t>
-  </si>
-  <si>
-    <t>0.896</t>
-  </si>
-  <si>
-    <t>0.928</t>
-  </si>
-  <si>
-    <t>0.504</t>
-  </si>
-  <si>
-    <t>results = model.train(</t>
-  </si>
-  <si>
-    <t>    data='../dataset_config.yaml',  # El nuevo nombre que le hemos dado</t>
-  </si>
-  <si>
-    <t>    epochs=100,</t>
-  </si>
-  <si>
-    <t>    imgsz=448,</t>
-  </si>
-  <si>
-    <t>    batch=16,</t>
-  </si>
-  <si>
-    <t>    mixup=0.5,    # Un toque de MixUp suele ayudar más en acero</t>
-  </si>
-  <si>
-    <t>    hsv_h=0.015,   # Cambia el tono (color) un poco</t>
-  </si>
-  <si>
-    <t>    hsv_s=0.7,     # Cambia la saturación</t>
-  </si>
-  <si>
-    <t>    hsv_v=0.4,     # Cambia el brillo (muy útil para reflejos en el acero)</t>
-  </si>
-  <si>
-    <t>    degrees=10.0,  # Rota las imágenes hasta 10 grados (recalcula etiquetas solo)</t>
-  </si>
-  <si>
-    <t>    translate=0.1, # Mueve la imagen un 10% (mueve etiquetas también)</t>
-  </si>
-  <si>
-    <t>    scale=0.5,     # Zoom hacia afuera/adentro</t>
-  </si>
-  <si>
-    <t>    flipud=0.5,    # Volteo vertical (50% de probabilidad)</t>
-  </si>
-  <si>
-    <t>    fliplr=0.5,    # Volteo horizontal (50% de probabilidad)</t>
-  </si>
-  <si>
-    <t>    mosaic=1.0,    # Mezcla 4 imágenes en una (ya lo hacía, pero aquí lo confirmas)</t>
-  </si>
-  <si>
-    <t>    name='tfm_steel_aimgsz_448_mixup_0-5',</t>
-  </si>
-  <si>
-    <t>    device=0</t>
-  </si>
-  <si>
-    <t>)</t>
-  </si>
-  <si>
-    <t>Config</t>
+    <t>0.379</t>
+  </si>
+  <si>
+    <t>0.554</t>
+  </si>
+  <si>
+    <t>0.251</t>
+  </si>
+  <si>
+    <t>0.399</t>
+  </si>
+  <si>
+    <t>0.133</t>
+  </si>
+  <si>
+    <t>0.618</t>
+  </si>
+  <si>
+    <t>0.731</t>
+  </si>
+  <si>
+    <t>0.734</t>
+  </si>
+  <si>
+    <t>0.349</t>
+  </si>
+  <si>
+    <t>0.781</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>0.939</t>
+  </si>
+  <si>
+    <t>0.591</t>
+  </si>
+  <si>
+    <t>0.767</t>
+  </si>
+  <si>
+    <t>0.797</t>
+  </si>
+  <si>
+    <t>0.859</t>
+  </si>
+  <si>
+    <t>0.477</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>0.627</t>
+  </si>
+  <si>
+    <t>0.612</t>
+  </si>
+  <si>
+    <t>0.302</t>
+  </si>
+  <si>
+    <t>0.609</t>
+  </si>
+  <si>
+    <t>0.839</t>
+  </si>
+  <si>
+    <t>0.828</t>
+  </si>
+  <si>
+    <t>0.42</t>
   </si>
 </sst>
 </file>
@@ -234,7 +297,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +319,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -295,6 +364,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,25 +700,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2383FF-B24A-4DF5-9655-B84368EDFCD8}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="73.5703125" customWidth="1"/>
+    <col min="11" max="11" width="72" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="21" max="21" width="76.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>0</v>
@@ -670,10 +756,58 @@
       <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>7</v>
@@ -684,22 +818,70 @@
       <c r="E4" s="6">
         <v>442</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F4" s="6">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="6">
+        <v>180</v>
+      </c>
+      <c r="O4" s="6">
+        <v>442</v>
+      </c>
+      <c r="P4" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="X4" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>442</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
@@ -710,22 +892,70 @@
       <c r="E5" s="6">
         <v>74</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" s="6">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="6">
+        <v>180</v>
+      </c>
+      <c r="O5" s="6">
+        <v>74</v>
+      </c>
+      <c r="P5" s="6">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="S5" s="6">
+        <v>0.182</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="X5" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>74</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>9</v>
@@ -736,22 +966,70 @@
       <c r="E6" s="6">
         <v>113</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F6" s="6">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="6">
+        <v>180</v>
+      </c>
+      <c r="O6" s="6">
+        <v>113</v>
+      </c>
+      <c r="P6" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>113</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>10</v>
@@ -762,21 +1040,71 @@
       <c r="E7" s="6">
         <v>80</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="F7" s="6">
+        <v>0.77700000000000002</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="6">
+        <v>180</v>
+      </c>
+      <c r="O7" s="6">
+        <v>80</v>
+      </c>
+      <c r="P7" s="6">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="S7" s="6">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="X7" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>80</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC7" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
@@ -786,23 +1114,69 @@
       <c r="E8" s="6">
         <v>33</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="6" t="s">
+      <c r="F8" s="6">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.496</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8" s="6">
+        <v>180</v>
+      </c>
+      <c r="O8" s="6">
         <v>33</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="P8" s="6">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0.78</v>
+      </c>
+      <c r="S8" s="6">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="X8" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>33</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
       <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
@@ -812,22 +1186,68 @@
       <c r="E9" s="6">
         <v>75</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" s="6">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="M9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="6">
+        <v>180</v>
+      </c>
+      <c r="O9" s="6">
+        <v>75</v>
+      </c>
+      <c r="P9" s="6">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="S9" s="6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="X9" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>75</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC9" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>13</v>
@@ -838,76 +1258,510 @@
       <c r="E10" s="6">
         <v>67</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F10" s="6">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.504</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="6">
+        <v>180</v>
+      </c>
+      <c r="O10" s="6">
+        <v>67</v>
+      </c>
+      <c r="P10" s="6">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0.504</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="X10" s="6">
+        <v>180</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>67</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="U11" s="3"/>
+      <c r="W11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" s="8"/>
+      <c r="U14" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z15" s="8"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="P16" s="7">
+        <f>(P4-F4)/F4</f>
+        <v>-5.9334298118668492E-2</v>
+      </c>
+      <c r="Q16" s="7">
+        <f t="shared" ref="Q16:S22" si="0">(Q4-G4)/G4</f>
+        <v>1.4598540145985252E-2</v>
+      </c>
+      <c r="R16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.3717421124828544E-3</v>
+      </c>
+      <c r="S16" s="7">
+        <f t="shared" si="0"/>
+        <v>1.4888337468982505E-2</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC16" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" ref="P17:P22" si="1">(P5-F5)/F5</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="0"/>
+        <v>0.29571984435797671</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="0"/>
+        <v>-8.6448598130841076E-2</v>
+      </c>
+      <c r="S17" s="7">
+        <f t="shared" si="0"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="7" t="e">
+        <f>(Z5-P5)/P5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA17" s="7" t="e">
+        <f t="shared" ref="AA17:AA23" si="2">(AA5-Q5)/Q5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AB17" s="7" t="e">
+        <f t="shared" ref="AB17:AB23" si="3">(AB5-R5)/R5</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC17" s="7" t="e">
+        <f t="shared" ref="AC17:AC23" si="4">(AC5-S5)/S5</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.13522012578616346</v>
+      </c>
+      <c r="Q18" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.9126213592233035E-2</v>
+      </c>
+      <c r="S18" s="7">
+        <f t="shared" si="0"/>
+        <v>-3.4031413612565474E-2</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="Y18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="7" t="e">
+        <f t="shared" ref="Z18:Z23" si="5">(Z6-P6)/P6</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA18" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AB18" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC18" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="O19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="P19" s="7">
+        <f t="shared" si="1"/>
+        <v>5.1480051480051522E-3</v>
+      </c>
+      <c r="Q19" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.7027027027027049E-2</v>
+      </c>
+      <c r="R19" s="7">
+        <f t="shared" si="0"/>
+        <v>1.0787486515641865E-3</v>
+      </c>
+      <c r="S19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="Y19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA19" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AB19" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC19" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P20" s="7">
+        <f t="shared" si="1"/>
+        <v>-4.0141676505312904E-2</v>
+      </c>
+      <c r="Q20" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.13055954088952651</v>
+      </c>
+      <c r="R20" s="7">
+        <f t="shared" si="0"/>
+        <v>-3.8314176245210761E-3</v>
+      </c>
+      <c r="S20" s="7">
+        <f t="shared" si="0"/>
+        <v>-2.2177419354838728E-2</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="Y20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA20" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AB20" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC20" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" s="7">
+        <f t="shared" si="1"/>
+        <v>2.8268551236749144E-2</v>
+      </c>
+      <c r="Q21" s="7">
+        <f t="shared" si="0"/>
+        <v>0.21639344262295082</v>
+      </c>
+      <c r="R21" s="7">
+        <f t="shared" si="0"/>
+        <v>0.18568994889267459</v>
+      </c>
+      <c r="S21" s="7">
+        <f t="shared" si="0"/>
+        <v>0.1775362318840579</v>
+      </c>
+      <c r="U21" s="3"/>
+      <c r="Y21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z21" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA21" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AB21" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC21" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="7">
+        <f t="shared" si="1"/>
+        <v>-0.18181818181818171</v>
+      </c>
+      <c r="Q22" s="7">
+        <f t="shared" si="0"/>
+        <v>-3.6830357142857172E-2</v>
+      </c>
+      <c r="R22" s="7">
+        <f t="shared" si="0"/>
+        <v>-4.6336206896551761E-2</v>
+      </c>
+      <c r="S22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>59</v>
+      <c r="Y22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z22" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA22" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AB22" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AC22" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z23" s="7" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA23" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB23" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC23" s="7" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U24" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>